--- a/Compititor's_Price/IKO_Prices/IKO_Prices_14-04-2026.xlsx
+++ b/Compititor's_Price/IKO_Prices/IKO_Prices_14-04-2026.xlsx
@@ -498,17 +498,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>£12.76</t>
+          <t>£12.33</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>£12.76</t>
+          <t>£12.33</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>£12.76</t>
+          <t>£12.33</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -555,17 +555,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>£14.51</t>
+          <t>£14.06</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>£14.51</t>
+          <t>£14.06</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>£14.51</t>
+          <t>£14.06</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -612,17 +612,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>£18.51</t>
+          <t>£18.33</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>£18.51</t>
+          <t>£18.33</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>£18.51</t>
+          <t>£18.33</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -669,17 +669,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>£18.92</t>
+          <t>£18.44</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>£18.92</t>
+          <t>£18.44</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>£18.92</t>
+          <t>£18.44</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -726,17 +726,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£23.91</t>
+          <t>£23.65</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>£23.91</t>
+          <t>£23.65</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>£23.91</t>
+          <t>£23.65</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1068,17 +1068,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>£41.52</t>
+          <t>£38.76</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>£41.52</t>
+          <t>£38.76</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>£41.52</t>
+          <t>£38.76</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1125,17 +1125,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>£40.49</t>
+          <t>£40.15</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>£40.49</t>
+          <t>£40.15</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>£40.49</t>
+          <t>£40.15</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1182,17 +1182,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>£49.76</t>
+          <t>£49.00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>£49.76</t>
+          <t>£49.00</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>£49.76</t>
+          <t>£49.00</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
